--- a/tabla_maestra_irpf_2025_menendez_pidal.xlsx
+++ b/tabla_maestra_irpf_2025_menendez_pidal.xlsx
@@ -5,14 +5,16 @@
     <sheet name="01_ingresos_2025" sheetId="1" r:id="rId1"/>
     <sheet name="02_gastos_recurrentes_2025" sheetId="2" r:id="rId2"/>
     <sheet name="03_hipoteca_intereses" sheetId="3" r:id="rId3"/>
-    <sheet name="04_seguro" sheetId="4" r:id="rId4"/>
-    <sheet name="05_reforma_facturas" sheetId="5" r:id="rId5"/>
-    <sheet name="06_reforma_pagos" sheetId="6" r:id="rId6"/>
-    <sheet name="07_cruce_factura_pago" sheetId="7" r:id="rId7"/>
-    <sheet name="08_mobiliario_equipamiento" sheetId="8" r:id="rId8"/>
-    <sheet name="09_amortizaciones" sheetId="9" r:id="rId9"/>
-    <sheet name="10_gastos_dudosos_excluidos" sheetId="10" r:id="rId10"/>
-    <sheet name="11_riesgos_y_pendientes" sheetId="11" r:id="rId11"/>
+    <sheet name="03b_contexto_hipoteca" sheetId="4" r:id="rId4"/>
+    <sheet name="04_seguro" sheetId="5" r:id="rId5"/>
+    <sheet name="05_reforma_facturas" sheetId="6" r:id="rId6"/>
+    <sheet name="06_reforma_pagos_obra" sheetId="7" r:id="rId7"/>
+    <sheet name="06b_pagos_descartados_o_dudosos" sheetId="8" r:id="rId8"/>
+    <sheet name="07_cruce_factura_pago" sheetId="9" r:id="rId9"/>
+    <sheet name="08_mobiliario_equipamiento" sheetId="10" r:id="rId10"/>
+    <sheet name="09_amortizaciones" sheetId="11" r:id="rId11"/>
+    <sheet name="10_gastos_dudosos_excluidos" sheetId="12" r:id="rId12"/>
+    <sheet name="11_riesgos_y_pendientes" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -57,30 +59,50 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>periodo_o_fecha</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>pagador_o_grupo</t>
+          <t>periodo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t>pagador_real</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>rol</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>concepto</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
           <t>importe_eur</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>criterio_actual</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t>nivel_solidez</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -89,352 +111,676 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Andrea+Erick+Juanjo+Imad</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Andrea / Erick / Juanjo / Imad</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Inquilinos habitaciones</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cobro alquiler enero</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ingresos recurrentes detectados</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ingreso recurrente detectado</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Andrea+Erick+Juanjo+Imad</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Andrea / Erick / Juanjo / Imad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Inquilinos habitaciones</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cobro alquiler febrero</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ingresos recurrentes detectados</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ingreso recurrente detectado</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Andrea+Erick+Juanjo+Imad</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Andrea / Erick / Juanjo / Imad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Inquilinos habitaciones</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cobro alquiler marzo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>1245.00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ingresos recurrentes detectados</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ingreso recurrente detectado</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Andrea+Erick+Juanjo</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Andrea / Erick / Juanjo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Inquilinos habitaciones</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cobro alquiler abril</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>950.00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ingresos recurrentes detectados</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ingreso recurrente detectado</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Andrea+Erick+Juanjo</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Andrea / Erick / Juanjo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Inquilinos habitaciones</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cobro alquiler mayo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>950.00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ingresos recurrentes detectados</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ingreso recurrente detectado</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Andrea+Erick+Juanjo</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Andrea / Erick / Juanjo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Inquilinos habitaciones</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cobro alquiler junio</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>950.00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ingresos recurrentes detectados</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ingreso recurrente detectado</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Andrea+Erick</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Andrea / Erick</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Inquilinos habitaciones</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cobro alquiler julio</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>640.00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ingresos recurrentes detectados</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ingreso recurrente detectado</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lucia / cobro agrupado</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t/>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Excel 5436</t>
+          <t>Vacancia / revisar imputacion</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>Agosto sin ingreso detectado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobro agrupado del piso</t>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Excel 5436 + criterio a cerrar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Explicitar vacancia o posible imputación de renta si aplica</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lucia / cobro agrupado</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1200.00</t>
+          <t/>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Excel 5436</t>
+          <t>Vacancia / revisar imputacion</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>Septiembre sin ingreso detectado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobro agrupado del piso</t>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Excel 5436 + criterio a cerrar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Explicitar vacancia o posible imputación de renta si aplica</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lucia / cobro agrupado</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Lucia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Intermediaria / cobro agrupado</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cobro agrupado octubre</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>1200.00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Cobro agrupado del piso</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Separado pagador real de su rol</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lucia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Intermediaria / cobro agrupado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cobro agrupado noviembre</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1200.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Excel 5436</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Separado pagador real de su rol</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lucia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Intermediaria / cobro agrupado</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cobro agrupado diciembre</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1200.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Excel 5436</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Separado pagador real de su rol</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Total ingresos 2025</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>10825.00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Base fiscal v5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Total ingresos 2025 detectados</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Suma revisada</t>
         </is>
       </c>
     </row>
@@ -448,25 +794,40 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>concepto</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t>proveedor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
           <t>importe_eur</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t>bloque</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>criterio_actual</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>criterio_hacienda</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>nivel_soporte</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -475,216 +836,630 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Telefonia/internet 2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>144.03</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gasto recurrente piso</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DUDOSO_OPCIONAL</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Razonable pero menos limpio</t>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mantenimiento cuenta 2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gasto recurrente piso</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DUDOSO_OPCIONAL</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Muy vinculado a la cuenta del piso pero discutible</t>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Seguro 135,28</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>135.28</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apunte en cuenta no fiable para el piso</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EXCLUIR_COMO_BASE_BUENA</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jero indicó que no usar como coste bueno del seguro del piso</t>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amazon enviados a Viator</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>325.36</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO_USAR</t>
+          <t>119.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Criterio fijado por Jero</t>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKEA ticket 0174981</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>369.21</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>4 bases tapizadas 120x190</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PENDIENTE_FLOJO</t>
+          <t>351.96</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ticket real, flojo</t>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Detalle de pedido con envio a Menendez Pidal; la factura visible es unitaria pero Jero confirma 4 unidades</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKEA ticket 0195936</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>142.21</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>Compra tienda IKEA ticket simplificado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PENDIENTE_FLOJO</t>
+          <t>369.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ticket real, flojo</t>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FLOJO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Limpieza Menendez Pidal x2</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>156.00</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Puesta a punto</t>
+          <t>Compra IKEA con entrega a Menendez Pidal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>579.16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sin soporte fino</t>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Direccion de envio a Menendez Pidal y detalle completo de articulos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Conceptos Menendez Pidal 52 ambiguos</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Compra tienda IKEA ticket simplificado</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>142.21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>PENDIENTE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Asociados al piso pero ambiguos</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FLOJO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Almohadas y protectores enviado a Viator</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>161.93</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fundas de almohada enviado a Viator</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>45.56</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Escobillas WC enviado a Viator</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10.48</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Posteres enviado a Viator</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>18.69</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rellenos de cojines enviado a Viator</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>36.80</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Microondas enviado a Viator</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>51.90</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>mobiliario_y_equipamiento</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CECOTEC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Frigorifico Bolero CoolMarket Combi 250 White E</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>329.00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>equipamiento_fijo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Equipamiento fijo, no base de reforma inmueble</t>
         </is>
       </c>
     </row>
@@ -698,220 +1473,938 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>tema</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>riesgo_o_pendiente</t>
+          <t>bloque</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>nivel</t>
+          <t>importe_o_base</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>accion_recomendada</t>
+          <t>fuente_o_soporte</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>nivel_cierre</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>observaciones</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IRPF 2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Seguro declarado en póliza como residencia habitual</t>
+          <t>BASE_INMUEBLE_COSTE_ADQUISICION</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>64000.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Revisar coherencia con alquiler por habitaciones</t>
+          <t>Escritura compraventa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No cerrar sola; falta gastos adquisición y exclusión suelo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IRPF 2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Superficie declarada al seguro 98 m2 vs 81,48 registrales/catastrales</t>
+          <t>BASE_INMUEBLE_VALOR_REFERENCIA_ITP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>71350.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Posible incoherencia a revisar antes de renovar</t>
+          <t>Modelo 600 / ITP</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Útil como contraste; cuidado con beneficio vivienda habitual</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IRPF 2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intereses 2025 con resumen anual bancario sin valor fiscal formal</t>
+          <t>SUELO_TASACION</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajo-Medio</t>
+          <t>25268.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Buena base operativa, pero mejorar si aparece certificado más formal</t>
+          <t>Tasación 26/06/2023</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Base para doble cálculo con tasación</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Reforma</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pagos contratista muy bien trazados pero cierre fiscal/documental final aún no cerrado</t>
+          <t>ITP_PAGADO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>2497.28</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tabla v2 ya distingue fuerte/provisional</t>
+          <t>Modelo 600</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gasto de adquisición capitalizable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reforma</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Importes exactos OBRAMAT no volcados aún en cruce final</t>
+          <t>BASE_AMORTIZABLE_INMUEBLE_METODO_TASACION</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>PENDIENTE_CALCULO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pendiente si se quiere afinado extremo</t>
+          <t>Compra + gastos - suelo tasación</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ABIERTO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Preparar cálculo 3% sin cerrarlo aquí</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reforma</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tickets IKEA simplificados flojos</t>
+          <t>BASE_AMORTIZABLE_INMUEBLE_METODO_CATASTRO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medio-Alto</t>
+          <t>PENDIENTE_CALCULO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mantener separados</t>
+          <t>Pendiente dato desglose suelo/construcción catastral</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ABIERTO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Añadir cuando se tenga porcentaje suelo exacto</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Renovación natural alrededor del 27/07/2026</t>
+          <t>BLOQUE_OBRAMAT_CUANTIFICADO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>6152.09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Revisar prima, uso y m2 antes de renovar</t>
+          <t>Facturas OBRAMAT extraídas</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ya cuantificado, pendiente separar reparación vs mejora</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Registro</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Falta nota simple actualizada postcompra si se quiere expediente redondo</t>
+          <t>BASE_MEJORA_REFORMA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bajo</t>
+          <t>PENDIENTE_SEPARAR_REPARACION_VS_MEJORA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No bloquea análisis IRPF 2025</t>
+          <t>Reforma 2023-2024 + OBRAMAT 6.152,09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ABIERTO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Separar lo que incrementa valor/utilidad y amortizar al 3%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estrategia documental</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Usar V5 fiscal como cifra base y v2 reforma como bloque soporte</t>
+          <t>BASE_MOBILIARIO_10PORCIENTO_FUERTE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>1736.12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CECOTEC + AMAZON + IKEA fuerte</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MEDIO-FUERTE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Va por su lado, no mezclar con reforma inmueble</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BASE_MOBILIARIO_10PORCIENTO_FLOJA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>511.42</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IKEA tickets simplificados</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FLOJO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mantener aparte</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2023-2027</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BOLSA_REPARACION_2023</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PENDIENTE_CLASIFICAR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reforma/pagos 2023 + OBRAMAT 2023</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ABIERTO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Si una parte es reparación, revisar arrastre 4 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-2028</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BOLSA_REPARACION_2024</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PENDIENTE_CLASIFICAR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Reforma/pagos 2024 + OBRAMAT 2024</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ABIERTO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Si una parte es reparación, revisar arrastre 4 años</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>ejercicio_devengo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>concepto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>importe_eur</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>criterio_actual</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Telefonía/internet 2025</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>144.03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gasto recurrente piso</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DUDOSO_OPCIONAL</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Razonable pero menos limpio</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mantenimiento cuenta 2025</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Gasto recurrente piso</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DUDOSO_OPCIONAL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vinculado a la cuenta del piso pero discutible</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Seguro 135,28 por identificar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>135.28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Movimiento en cuenta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EXCLUIR_HASTA_IDENTIFICAR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Único habitante injustificado claro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amazon enviados a Viator</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>325.36</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mobiliario/equipamiento</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NO_USAR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Criterio fijado por Jero</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IKEA ticket 0174981</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>369.21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mobiliario/equipamiento</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PENDIENTE_FLOJO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ticket real, flojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IKEA ticket 0195936</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>142.21</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mobiliario/equipamiento</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PENDIENTE_FLOJO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ticket real, flojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Limpieza Menendez Pidal x2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>156.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Puesta a punto</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sin soporte fino</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Conceptos Menendez Pidal 52 ambiguos</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>170.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Satélite</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asociados al piso pero ambiguos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>ejercicio_devengo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>riesgo_o_pendiente</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>accion_recomendada</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ITP aplicado con beneficio vivienda habitual</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Revisar coherencia con destino real posterior y narrativa documental</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Contratos Antonio Cano</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Revisar encaje documental y efecto en ingresos/ocupación</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Calificación reparación vs mejora</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Separar con criterio técnico-fiscal porque cambia deducción/amortización</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dependencia de lo declarado en 2023/2024</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>La estrategia 2025 debe ser coherente con años previos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Seguro declarado como residencia habitual</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Revisar coherencia con alquiler por habitaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Superficie seguro 98 m2 vs 81,48 m2 registrales/catastrales</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Corregir en próxima renovación si procede</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Importes OBRAMAT ya extraídos pero falta clasificación técnica</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Resolver reparación vs mejora antes del cierre definitivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tickets IKEA simplificados flojos</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Medio-Alto</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Intentar factura nominativa o dejarlos fuera</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Falta nota simple actualizada postcompra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Bajo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Buen punto de partida para Claude/ChatGPT</t>
+          <t>No bloquea IRPF 2025, pero redondea expediente</t>
         </is>
       </c>
     </row>
@@ -925,30 +2418,45 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
+          <t>ejercicio_devengo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
           <t>concepto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>importe_eur</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t>importe_bruto_eur</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>prorrateo_dias_arrendados_o_criterio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>importe_computable_irpf_2025_eur</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
           <t>criterio_inicial</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t>fuente</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t>nivel_solidez</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -957,30 +2465,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Agua</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>362.03</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100% alquiler</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>362.03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Deducible</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Recibos FCC Aqualia 2025</t>
         </is>
@@ -989,30 +2512,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Luz</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>633.50</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>100% alquiler</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>633.50</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Deducible</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Recibos electricidad 2025</t>
         </is>
@@ -1021,30 +2559,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Comunidad</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>240.00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100% alquiler</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>240.00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Deducible</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Excel 5436 + criterio confirmado</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>20 €/mes todo 2025</t>
         </is>
@@ -1053,30 +2606,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>IBI</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>256.26</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>100% alquiler</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>256.26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Deducible</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>PDF IBI 2025</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>FUERTE</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>IBI localizado</t>
         </is>
@@ -1085,30 +2653,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Seguro hogar prorrateado</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>331.36</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100% alquiler</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>331.36</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Deducible</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Poliza CASER trianual</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Póliza CASER trianual</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>MEDIO-FUERTE</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Prorrateo 994,08/3 por criterio economico</t>
         </is>
@@ -1117,64 +2700,141 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Telefonia/internet</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Telefonía/internet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>144.03</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100% alquiler si incluido en renta</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>144.03</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Dudoso/opcional</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Razonable si incluido en renta</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mantener abierto</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Mantenimiento cuenta</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>100% alquiler si cuenta exclusiva del piso</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Dudoso/opcional</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Excel 5436</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>MEDIO-BAJO</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Cuenta muy vinculada al piso</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mantener abierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Apunte seguro por identificar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>135.28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Excluido hasta identificar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Movimiento en cuenta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Posible gasto perdido; no usar hasta identificar su naturaleza</t>
         </is>
       </c>
     </row>
@@ -1188,7 +2848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>periodo_o_fecha</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
@@ -1245,7 +2905,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mejor dato financiero disponible para 2025</t>
+          <t>Mejor dato financiero disponible para IRPF 2025</t>
         </is>
       </c>
     </row>
@@ -1309,71 +2969,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dato financiero, no gasto corriente deducible</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cuota marzo 2026 intereses</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>107.39</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Recibo hipoteca 27/03/2026</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Foto real de reparto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cuota mayo 2026 intereses</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>114.58</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Recibo hipoteca 27/05/2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Foto real de reparto</t>
+          <t>Dato financiero separado, no gasto corriente deducible</t>
         </is>
       </c>
     </row>
@@ -1387,55 +2983,30 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>producto</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>poliza</t>
+          <t>concepto</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>fecha_efecto</t>
+          <t>importe_eur</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>fecha_vencimiento</t>
+          <t>fuente</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t>continente_eur</t>
+          <t>nivel_solidez</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t>contenido_eur</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t>rc_general_eur</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t>coste_trianual_visible_eur</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t>coste_anual_equivalente_eur</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t>fuente</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -1444,57 +3015,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASER Hogar Proteccion / Hogar Trianual Clientes</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96560081</t>
+          <t>Cuota marzo 2026 intereses</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>107.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>Recibo hipoteca 27/03/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75000.00</t>
+          <t>FUERTE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18000.00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>300000.00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>994.08</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>331.36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Condiciones particulares + recibo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Uso declarado residencia habitual; 98 m2 declarados; revisar renovacion julio 2026</t>
+          <t>Contexto de reparto interés/capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cuota marzo 2026 capital amortizado</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>113.13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Recibo hipoteca 27/03/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Contexto de reparto interés/capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cuota mayo 2026 intereses</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Recibo hipoteca 27/05/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Contexto de reparto interés/capital</t>
         </is>
       </c>
     </row>
@@ -1508,50 +3118,60 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>fecha</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>proveedor</t>
+          <t>producto</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>subbloque</t>
+          <t>poliza</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>concepto</t>
+          <t>fecha_efecto</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t>documento</t>
+          <t>fecha_vencimiento</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t>pedido_o_ref</t>
+          <t>continente_eur</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t>importe_total_eur</t>
+          <t>contenido_eur</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t>usar_hacienda</t>
+          <t>rc_general_eur</t>
         </is>
       </c>
       <c r="I1" t="inlineStr" s="1">
         <is>
-          <t>nivel_soporte</t>
+          <t>coste_trianual_visible_eur</t>
         </is>
       </c>
       <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t>coste_anual_equivalente_eur</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -1560,988 +3180,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OBRAMAT</t>
+          <t>CASER Hogar Proteccion / Hogar Trianual Clientes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>obra_reforma</t>
+          <t>96560081</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Materiales reforma pedido 228131</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Factura 003-0011-399514</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>228131</t>
+          <t>75000.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t/>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>994.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2023-12-07</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OBRAMAT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>obra_reforma</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Materiales reforma pedido 228543</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Factura 003-0012-404381</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>228543</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>OBRAMAT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>obra_reforma</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Materiales reforma pedido 229407</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Factura 003-0001-424413</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>229407</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2024-02-08</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>OBRAMAT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>obra_reforma</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Materiales reforma pedido 230379</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Factura 003-0002-437264</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>230379</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>equipamiento_fijo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Frigorifico Bolero CoolMarket Combi 250 White E</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Factura 259006389</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>256CEC-259006389</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>329.00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Factura 259006390</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>256CEC-259006390</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Factura 259006391</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>256CEC-259006391</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Factura 259006392</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>256CEC-259006392</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 4</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Factura 259006393</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>256CEC-259006393</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4 bases tapizadas 120x190</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Pedido Amazon + factura ES421LCLRAEUS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>402-6402422-7836305</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>351.96</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Detalle de pedido con envio a Menendez Pidal; la factura visible es unitaria pero Jero confirma 4 unidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IKEA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Compra tienda IKEA ticket simplificado</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Factura simplificada SIM_691_2024/0174981</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SIM_691_2024/0174981</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>369.21</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>FLOJO</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IKEA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Compra IKEA con entrega a Menendez Pidal</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Factura ESSIM24000000034880</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1443737502</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>579.16</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Direccion de envio a Menendez Pidal y detalle completo de articulos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IKEA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Compra tienda IKEA ticket simplificado</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Factura simplificada SIM_691_2024/0195936</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SIM_691_2024/0195936</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>142.21</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>FLOJO</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Almohadas y protectores enviado a Viator</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLPAEUS</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>404-8694384-4720359</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>161.93</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fundas de almohada enviado a Viator</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLQAEUS</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>404-2782946-5035510</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>45.56</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Escobillas WC enviado a Viator</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLOAEUS</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>404-6553842-1560302</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Posteres enviado a Viator</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Factura DS-ASE-INV-ES-2024-62121755</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>404-8326125-2181120</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Rellenos de cojines enviado a Viator</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Factura SIM-INV-ES-1461148515-2024-688</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>404-9365037-7246721</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>36.80</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Microondas enviado a Viator</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLNAEUS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>402-6883202-0465961</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>51.90</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
+          <t>331.36</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Póliza + recibo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Uso declarado residencia habitual; 98 m2 declarados; revisar coherencia y renovación 2026</t>
         </is>
       </c>
     </row>
@@ -2555,40 +3249,60 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
+          <t>ejercicio_devengo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>contraparte</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t>proveedor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>subbloque</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
           <t>concepto</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>importe_eur</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t>cuenta</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t>soporte</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t>criterio_hacienda</t>
+          <t>documento</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>pedido_o_ref</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t>importe_total_eur</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t>usar_hacienda</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t>nivel_soporte</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -2597,798 +3311,1178 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inicio obra (pago 1/2)</t>
+          <t>OBRAMAT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>reforma</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>obra_reforma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Justificante + extracto</t>
+          <t>Materiales reforma pedido 228131</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 003-0011-399514</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pago directo contratista</t>
+          <t>228131</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4803.37</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inicio obra (pago 2/2)</t>
+          <t>OBRAMAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>reforma</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>obra_reforma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Justificante + extracto</t>
+          <t>Materiales reforma pedido 228543</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 003-0012-404381</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pago directo contratista</t>
+          <t>228543</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>161.13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reforma pago intermedio n2</t>
+          <t>OBRAMAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1301.74</t>
+          <t>reforma</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>obra_reforma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Justificante + extracto</t>
+          <t>Materiales reforma pedido 229407</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 003-0001-424413</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pago directo contratista</t>
+          <t>229407</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1037.22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pago obra intermedio Menendez Pidal</t>
+          <t>OBRAMAT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>reforma</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>obra_reforma</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Justificante + extracto</t>
+          <t>Materiales reforma pedido 230379</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 003-0002-437264</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pago directo contratista</t>
+          <t>230379</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>150.37</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pago intermedio</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>reforma</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>equipamiento_fijo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Frigorifico Bolero CoolMarket Combi 250 White E</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 259006389</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Falta justificante individual</t>
+          <t>256CEC-259006389</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>329.00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Obra pago 5</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1900.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Justificante + extracto</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 259006390</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pago directo contratista</t>
+          <t>256CEC-259006390</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>119.00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Obra pago 6</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Justificante + extracto</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 259006391</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pago directo contratista</t>
+          <t>256CEC-259006391</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>119.00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Juan Sebastián Beltrán Ramírez</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Final obra pago</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4835.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Justificante + extracto</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SI_PROVISIONAL</t>
+          <t>Factura 259006392</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pago directo contratista</t>
+          <t>256CEC-259006392</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>119.00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pluma materiales</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Colchon Flow Viscocare 1900 120x190 unidad 4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura 259006393</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Probable material</t>
+          <t>256CEC-259006393</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>119.00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Compra fontaneria</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>4 bases tapizadas 120x190</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Pedido Amazon + factura ES421LCLRAEUS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Probable material</t>
+          <t>402-6402422-7836305</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>351.96</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Detalle de pedido con envio a Menendez Pidal; la factura visible es unitaria pero Jero confirma 4 unidades</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pladur</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Compra tienda IKEA ticket simplificado</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Factura simplificada SIM_691_2024/0174981</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SIM_691_2024/0174981</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>369.21</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>PENDIENTE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Probable material</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FLOJO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Leroy Merlin</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Leroy Merlin compra</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>136.39</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Compra IKEA con entrega a Menendez Pidal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura ESSIM24000000034880</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Probable material</t>
+          <t>1443737502</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>579.16</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Direccion de envio a Menendez Pidal y detalle completo de articulos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LEROY merlin obra</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>71.64</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Compra tienda IKEA ticket simplificado</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Factura simplificada SIM_691_2024/0195936</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SIM_691_2024/0195936</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>142.21</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>PENDIENTE</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Probable material</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>FLOJO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Centroled</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Almohadas y protectores enviado a Viator</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura ES421LCLPAEUS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Importe pequeño material</t>
+          <t>404-8694384-4720359</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>161.93</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Puerta</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>325.45</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Fundas de almohada enviado a Viator</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura ES421LCLQAEUS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Elemento fijo probable</t>
+          <t>404-2782946-5035510</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>45.56</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Limpieza Menendez Pidal</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>78.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Escobillas WC enviado a Viator</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura ES421LCLOAEUS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Puesta a punto</t>
+          <t>404-6553842-1560302</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10.48</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Limpieza Menendez Pidal</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>78.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Posteres enviado a Viator</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura DS-ASE-INV-ES-2024-62121755</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Puesta a punto</t>
+          <t>404-8326125-2181120</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>18.69</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Menendez Pidal 52</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Rellenos de cojines enviado a Viator</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura SIM-INV-ES-1461148515-2024-688</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Concepto ambiguo</t>
+          <t>404-9365037-7246721</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>36.80</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>No identificado</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Menendez Pidal 52</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>mobiliario_y_equipamiento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Extracto</t>
+          <t>Microondas enviado a Viator</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>Factura ES421LCLNAEUS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Concepto ambiguo</t>
+          <t>402-6883202-0465961</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>51.90</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PROPIO_PERO_EXCLUIDO</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
         </is>
       </c>
     </row>
@@ -3402,30 +4496,45 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>bloque</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>descripcion</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t>contraparte</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>concepto</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
           <t>importe_eur</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>estado_cruce</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t>nivel_solidez</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>cuenta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>soporte</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>criterio_hacienda</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -3434,224 +4543,376 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Contratista principal</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pagos directos a Juan Sebastián Beltrán Ramírez</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16336.74</t>
+          <t>Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No cruzado todavía a factura fiscal final cerrada</t>
+          <t>Inicio obra (pago 1/2)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MEDIO-FUERTE</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nucleo duro de pagos confirmados</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Justificante + extracto</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pago directo contratista</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OBRAMAT</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Facturas 228131/228543/229407/230379</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hay soporte fuerte de factura, falta vincular importes exactos en esta tabla</t>
+          <t>Inicio obra (pago 2/2)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Usable para Hacienda</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Justificante + extracto</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pago directo contratista</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CECOTEC</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Frigorifico + 4 colchones</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>805.00</t>
+          <t>Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cruzado por factura nominativa</t>
+          <t>Reforma pago intermedio n2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>1301.74</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Usable fuerte</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Justificante + extracto</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Descuadre de 1,74 € a explicar frente a cierres redondos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 bases tapizadas</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>351.96</t>
+          <t>Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cruzado por pedido/factura</t>
+          <t>Pago obra intermedio Menendez Pidal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Usable fuerte</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Justificante + extracto</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pago directo contratista</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKEA fuerte</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pedido 1443737502</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>579.16</t>
+          <t>Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruzado por factura/entrega</t>
+          <t>Pago intermedio</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Usable fuerte</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Falta justificante individual</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKEA flojo</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tickets 0174981 y 0195936</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>511.42</t>
+          <t>Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Documento real pero flojo</t>
+          <t>Obra pago 5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FLOJO</t>
+          <t>1900.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pendiente mejora o criterio</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Justificante + extracto</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pago directo contratista</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amazon Viator</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pedidos enviados a Viator</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>325.36</t>
+          <t>Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cruzado y excluido</t>
+          <t>Obra pago 6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FUERTE</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No usar por criterio fijado</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Justificante + extracto</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pago directo contratista</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Juan Sebastián Beltrán Ramírez</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Final obra pago</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4835.00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Justificante + extracto</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI_PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pago directo contratista</t>
         </is>
       </c>
     </row>
@@ -3665,30 +4926,45 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>proveedor</t>
+          <t>ejercicio_devengo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>descripcion</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t>contraparte</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>concepto</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
           <t>importe_eur</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>bloque</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>cuenta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>soporte</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t>criterio_hacienda</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -3697,224 +4973,517 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CECOTEC</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frigorifico Bolero CoolMarket Combi 250 White E</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>329.00</t>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Equipamiento fijo</t>
+          <t>Pluma materiales</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SI_FUERTE</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Factura nominativa</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Probable material; fuera del núcleo de pagos de obra</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CECOTEC</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 colchones Flow Viscocare 1900 120x190</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>476.00</t>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>Compra fontaneria</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SI_FUERTE</t>
+          <t>52.12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 facturas nominativas</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Probable material; fuera del núcleo de pagos de obra</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 bases tapizadas 120x190</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>351.96</t>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>Pladur</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SI_FUERTE</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pedido reforzado por Jero</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Probable material; fuera del núcleo de pagos de obra</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Compra con entrega a Menendez Pidal</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>579.16</t>
+          <t>Leroy Merlin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>Leroy Merlin compra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SI_FUERTE</t>
+          <t>136.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Factura fuerte</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Probable material; fuera del núcleo de pagos de obra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ticket simplificado SIM_691_2024/0174981</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>369.21</t>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>LEROY merlin obra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PENDIENTE_FLOJO</t>
+          <t>71.64</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Soporte flojo</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Probable material; fuera del núcleo de pagos de obra</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ticket simplificado SIM_691_2024/0195936</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>142.21</t>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>Centroled</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PENDIENTE_FLOJO</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Soporte flojo</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Importe pequeño material</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMAZON</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pedidos enviados a Viator</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>325.36</t>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento</t>
+          <t>Puerta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NO_USAR</t>
+          <t>325.45</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Excluir por criterio ya fijado</t>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Elemento fijo probable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Limpieza Menendez Pidal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>78.00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Puesta a punto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Limpieza Menendez Pidal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>78.00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Puesta a punto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Menendez Pidal 52</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Concepto ambiguo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Menendez Pidal 52</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Extracto</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Concepto ambiguo</t>
         </is>
       </c>
     </row>
@@ -3928,25 +5497,35 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
+          <t>ejercicio_devengo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
           <t>bloque</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>importe_o_base</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>tipo_de_lectura</t>
+          <t>descripcion</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>fuente_o_soporte</t>
+          <t>importe_eur</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>estado_cruce</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>nivel_solidez</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t>observaciones</t>
         </is>
@@ -3955,189 +5534,259 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Inmueble</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Base amortizable no cerrada</t>
+          <t>OBRA_CONTRATISTA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABIERTO</t>
+          <t>Pagos directos a Juan Sebastián Beltrán Ramírez</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Usar esta hoja como preparatoria para analisis Claude/ChatGPT</t>
+          <t>16336.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Falta decidir base exacta excluyendo suelo y ajustando criterios</t>
+          <t>Cruzado a pagos, pendiente de resolver cierre fiscal/documental final</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MEDIO-FUERTE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No dejarlo en n/d permanente</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hipoteca principal</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1222.48</t>
+          <t>OBRAMAT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dato financiero no deducible corriente</t>
+          <t>Facturas 228131 / 228543 / 229407 / 230379</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cuota 2025 2646,24 - intereses 1423,76</t>
+          <t>6152.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Separado solo como referencia</t>
+          <t>Importes TTI ya extraídos de PDF; falta decidir reparación vs mejora</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hueco principal ya cuantificado</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reforma principal</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16336.74</t>
+          <t>CECOTEC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Base potencial a analizar</t>
+          <t>Frigorífico + 4 colchones</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pagos confirmados al contratista</t>
+          <t>805.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No cerrada fiscalmente</t>
+          <t>Cruzado por factura nominativa sustitutiva</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Conservar tickets originales por fecha de emisión 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Reforma ampliada razonable</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18072.86</t>
+          <t>AMAZON</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Base potencial a analizar</t>
+          <t>4 bases tapizadas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Obra principal + bloque fuerte adicional</t>
+          <t>351.96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No cerrar sin criterio fiscal</t>
+          <t>Cruzado por pedido/factura</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Usable fuerte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mobiliario/equipamiento fuerte</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1736.12</t>
+          <t>IKEA_FUERTE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Base potencial a analizar</t>
+          <t>Pedido 1443737502</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CECOTEC + AMAZON bases + IKEA fuerte</t>
+          <t>579.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>No cerrar sin criterio fiscal</t>
+          <t>Cruzado por factura/entrega</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Usable fuerte</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IKEA flojo</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>IKEA_FLOJO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tickets 0174981 y 0195936</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>511.42</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Base dudosa</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tickets simplificados</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mantener abierta</t>
+          <t>Documento real pero flojo; intentar nominativas</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FLOJO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pendiente mejora</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Observacion general</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t/>
+          <t>AMAZON_EXCLUIDO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A + C separadas por petición de Jero</t>
+          <t>Pedidos enviados a Viator</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Esta hoja queda deliberadamente abierta para análisis posterior</t>
+          <t>325.36</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No calcular cifra final automática</t>
+          <t>Cruzado y excluido</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FUERTE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No usar por criterio fijado</t>
         </is>
       </c>
     </row>

--- a/tabla_maestra_irpf_2025_menendez_pidal.xlsx
+++ b/tabla_maestra_irpf_2025_menendez_pidal.xlsx
@@ -2186,230 +2186,296 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t>ejercicio_devengo</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>riesgo_o_pendiente</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t>nivel</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>accion_recomendada</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ITP aplicado con beneficio vivienda habitual</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Revisar coherencia con destino real posterior y narrativa documental</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Contratos Antonio Cano</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Revisar encaje documental y efecto en ingresos/ocupación</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Calificación reparación vs mejora</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Separar con criterio técnico-fiscal porque cambia deducción/amortización</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dependencia de lo declarado en 2023/2024</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>La estrategia 2025 debe ser coherente con años previos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Seguro declarado como residencia habitual</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Revisar coherencia con alquiler por habitaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Superficie seguro 98 m2 vs 81,48 m2 registrales/catastrales</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Corregir en próxima renovación si procede</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Importes OBRAMAT ya extraídos pero falta clasificación técnica</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Resolver reparación vs mejora antes del cierre definitivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Tickets IKEA simplificados flojos</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Medio-Alto</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Intentar factura nominativa o dejarlos fuera</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Falta nota simple actualizada postcompra</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>No bloquea IRPF 2025, pero redondea expediente</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>ejercicio_devengo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>riesgo_o_pendiente</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>nivel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>accion_recomendada</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ITP aplicado con beneficio vivienda habitual</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Alto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Revisar coherencia con destino real posterior y narrativa documental</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Contratos Antonio Cano</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Alto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Revisar encaje documental y efecto en ingresos/ocupación</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Calificación reparación vs mejora</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Alto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Separar con criterio técnico-fiscal porque cambia deducción/amortización</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Dependencia de lo declarado en 2023/2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Alto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>La estrategia 2025 debe ser coherente con años previos</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Seguro declarado como residencia habitual</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medio</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Revisar coherencia con alquiler por habitaciones</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Superficie seguro 98 m2 vs 81,48 m2 registrales/catastrales</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medio</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Corregir en próxima renovación si procede</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Importes OBRAMAT ya extraídos pero falta clasificación técnica</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medio</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Resolver reparación vs mejora antes del cierre definitivo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Tickets IKEA simplificados flojos</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medio-Alto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Intentar factura nominativa o dejarlos fuera</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Falta nota simple actualizada postcompra</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Bajo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>No bloquea IRPF 2025, pero redondea expediente</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Ingreso puntual no recurrente (fianza + arranque agosto con mediación)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MEDIO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Jero aclaró que los 1.412 € se leen como 1.200 € de fianza + 212 € de ingreso real para él, con 600 € absorbidos por la inmobiliaria por medio mes de gestión. Mantener 212 € como ingreso inicial de Jero y dejar septiembre como transición no del todo cerrada por habitación.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT: anticipos 398765, 404208, 421861 y 436986 localizados</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medio</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>No sumarlos además de las facturas de entrega, porque replican el mismo TTI de los pedidos 228131, 228543, 229407 y 230379; usarlos como refuerzo documental y trazabilidad de pago.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2025</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT: compras adicionales omitidas ya localizadas parcialmente</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Medio</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Valorar incorporación separada de 404213 (80,19 €), 407792 (21,90 €), 452497 (39,53 €) y 452516 (135,00 €). Falta concretar si existe quinta omitida adicional o si el conteo del usuario incluía también el anticipo 404208.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3244,1250 +3310,1746 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t>ejercicio_devengo</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>fecha</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t>proveedor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>bloque</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t>subbloque</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t>concepto</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t>documento</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t>pedido_o_ref</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t>importe_total_eur</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t>usar_hacienda</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t>nivel_soporte</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr" s="1">
-        <is>
-          <t>observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2023-11-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OBRAMAT</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>reforma</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>obra_reforma</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Materiales reforma pedido 228131</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Factura 003-0011-399514</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>228131</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4803.37</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2023-12-07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OBRAMAT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>reforma</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>obra_reforma</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Materiales reforma pedido 228543</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Factura 003-0012-404381</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>228543</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>161.13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OBRAMAT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>reforma</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>obra_reforma</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Materiales reforma pedido 229407</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Factura 003-0001-424413</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>229407</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1037.22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2024-02-08</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OBRAMAT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>reforma</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>obra_reforma</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Materiales reforma pedido 230379</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Factura 003-0002-437264</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>230379</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>150.37</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>reforma</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>equipamiento_fijo</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Frigorifico Bolero CoolMarket Combi 250 White E</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Factura 259006389</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>256CEC-259006389</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>329.00</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Factura 259006390</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>256CEC-259006390</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Factura 259006391</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>256CEC-259006391</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Factura 259006392</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>256CEC-259006392</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CECOTEC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Colchon Flow Viscocare 1900 120x190 unidad 4</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Factura 259006393</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>256CEC-259006393</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>119.00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>4 bases tapizadas 120x190</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pedido Amazon + factura ES421LCLRAEUS</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>402-6402422-7836305</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>351.96</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Detalle de pedido con envio a Menendez Pidal; la factura visible es unitaria pero Jero confirma 4 unidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>IKEA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Compra tienda IKEA ticket simplificado</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Factura simplificada SIM_691_2024/0174981</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>SIM_691_2024/0174981</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>369.21</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>FLOJO</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>IKEA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Compra IKEA con entrega a Menendez Pidal</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Factura ESSIM24000000034880</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1443737502</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>579.16</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>FUERTE</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Direccion de envio a Menendez Pidal y detalle completo de articulos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>IKEA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Compra tienda IKEA ticket simplificado</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Factura simplificada SIM_691_2024/0195936</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>SIM_691_2024/0195936</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>142.21</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>FLOJO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Almohadas y protectores enviado a Viator</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLPAEUS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>404-8694384-4720359</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>161.93</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Fundas de almohada enviado a Viator</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLQAEUS</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>404-2782946-5035510</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>45.56</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Escobillas WC enviado a Viator</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLOAEUS</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>404-6553842-1560302</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10.48</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Posteres enviado a Viator</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Factura DS-ASE-INV-ES-2024-62121755</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>404-8326125-2181120</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Rellenos de cojines enviado a Viator</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Factura SIM-INV-ES-1461148515-2024-688</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>404-9365037-7246721</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>36.80</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>mobiliario</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>mobiliario_y_equipamiento</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Microondas enviado a Viator</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Factura ES421LCLNAEUS</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>402-6883202-0465961</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>51.90</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>PROPIO_PERO_EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>ejercicio_devengo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>fecha</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>proveedor</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>bloque</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>subbloque</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>concepto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>documento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>pedido_o_ref</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>importe_total_eur</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>usar_hacienda</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>nivel_soporte</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L1" t="inlineStr" s="1">
+        <ns0:is>
+          <ns0:t>observaciones</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023-11-28</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>obra_reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Materiales reforma pedido 228131</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0011-399514</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>228131</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>4803.37</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023-12-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>obra_reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Materiales reforma pedido 228543</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0012-404381</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>228543</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>161.13</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-01-17</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>obra_reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Materiales reforma pedido 229407</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0001-424413</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>229407</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1037.22</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-02-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>obra_reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Materiales reforma pedido 230379</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0002-437264</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>230379</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>150.37</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura duplicada con titular NIF y direccion de Menendez Pidal; importe total TTI extraído por pdftotext de factura PDF</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-04-15</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CECOTEC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>equipamiento_fijo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Frigorifico Bolero CoolMarket Combi 250 White E</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 259006389</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>256CEC-259006389</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>329.00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-04-19</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CECOTEC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Colchon Flow Viscocare 1900 120x190 unidad 1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 259006390</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>256CEC-259006390</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>119.00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-04-19</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CECOTEC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Colchon Flow Viscocare 1900 120x190 unidad 2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 259006391</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>256CEC-259006391</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>119.00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-04-19</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CECOTEC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Colchon Flow Viscocare 1900 120x190 unidad 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 259006392</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>256CEC-259006392</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>119.00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-04-19</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CECOTEC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Colchon Flow Viscocare 1900 120x190 unidad 4</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 259006393</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>256CEC-259006393</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>119.00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa sustitutiva de simplificada; facturas sustitutivas/canje emitidas el 08/06/2026 para compras de 2024, conservar tickets originales</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-06-10</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AMAZON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>4 bases tapizadas 120x190</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Pedido Amazon + factura ES421LCLRAEUS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>402-6402422-7836305</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>351.96</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Detalle de pedido con envio a Menendez Pidal; la factura visible es unitaria pero Jero confirma 4 unidades</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-06-20</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IKEA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Compra tienda IKEA ticket simplificado</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura simplificada SIM_691_2024/0174981</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SIM_691_2024/0174981</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>369.21</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PENDIENTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FLOJO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-06-26</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IKEA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Compra IKEA con entrega a Menendez Pidal</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura ESSIM24000000034880</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1443737502</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>579.16</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Direccion de envio a Menendez Pidal y detalle completo de articulos</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-07-09</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IKEA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Compra tienda IKEA ticket simplificado</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura simplificada SIM_691_2024/0195936</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SIM_691_2024/0195936</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>142.21</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PENDIENTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FLOJO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Ticket real pero sin nombre NIF ni direccion visibles en el extracto compartido</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-07-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AMAZON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Almohadas y protectores enviado a Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura ES421LCLPAEUS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>404-8694384-4720359</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>161.93</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PROPIO_PERO_EXCLUIDO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-07-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AMAZON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Fundas de almohada enviado a Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura ES421LCLQAEUS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>404-2782946-5035510</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>45.56</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PROPIO_PERO_EXCLUIDO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-07-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AMAZON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Escobillas WC enviado a Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura ES421LCLOAEUS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>404-6553842-1560302</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>10.48</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PROPIO_PERO_EXCLUIDO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-07-11</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AMAZON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Posteres enviado a Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura DS-ASE-INV-ES-2024-62121755</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>404-8326125-2181120</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>18.69</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PROPIO_PERO_EXCLUIDO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="A19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-07-11</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AMAZON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Rellenos de cojines enviado a Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura SIM-INV-ES-1461148515-2024-688</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>404-9365037-7246721</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>36.80</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PROPIO_PERO_EXCLUIDO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="A20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-07-15</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AMAZON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>mobiliario_y_equipamiento</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Microondas enviado a Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura ES421LCLNAEUS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>402-6883202-0465961</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>51.90</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PROPIO_PERO_EXCLUIDO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Jero decide no usar en Hacienda al enviarse a Grupo Chemie Viator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="21">
+      <ns0:c r="A21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023-11-27</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>anticipo_pedido</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Anticipo pedido 228131</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0011-398765</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>228131</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>4803.37</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO_SEPARADO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real de anticipo. Mismo TTI que la factura de entrega 003-0011-399514; no sumar aparte para evitar duplicidad, usar solo como refuerzo documental del pedido 228131.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22">
+      <ns0:c r="A22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023-12-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>anticipo_pedido</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Anticipo pedido 228543</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0012-404208</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>228543</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>161.13</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO_SEPARADO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real de anticipo. Mismo TTI que la factura de entrega 003-0012-404381; no sumar aparte para evitar duplicidad, usar solo como refuerzo documental del pedido 228543.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="A23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-01-12</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>anticipo_pedido</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Anticipo pedido 229407</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0001-421861</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>229407</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1037.22</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO_SEPARADO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real de anticipo. Mismo TTI que la factura de entrega 003-0001-424413; no sumar aparte para evitar duplicidad, usar solo como refuerzo documental del pedido 229407.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="24">
+      <ns0:c r="A24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-02-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>anticipo_pedido</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Anticipo pedido 230379</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0002-436986</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>230379</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>150.37</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NO_SEPARADO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real de anticipo. Mismo TTI que la factura de entrega 003-0002-437264; no sumar aparte para evitar duplicidad, usar solo como refuerzo documental del pedido 230379.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="25">
+      <ns0:c r="A25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023-12-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>materiales_satélite</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Compra autónoma adicional Obramat</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0012-404213</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>404213</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>80.19</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PENDIENTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real no integrada en los 4 pedidos principales. Compra separada, plausible para la obra, pendiente de decidir si se incorpora al núcleo de reforma.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="26">
+      <ns0:c r="A26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2023-12-13</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>materiales_satélite</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Compra autónoma adicional Obramat</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0012-407792</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>407792</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>21.90</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PENDIENTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real no integrada en los 4 pedidos principales. Compra pequeña de escayola, plausible para la obra.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="27">
+      <ns0:c r="A27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-03-05</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>materiales_satélite</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Compra autónoma adicional Obramat</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0003-452497</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>452497</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>39.53</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PENDIENTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real no integrada en los 4 pedidos principales. Material eléctrico/plaqueado, plausible para remates de obra.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="28">
+      <ns0:c r="A28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2024-03-05</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>OBRAMAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>reforma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>materiales_satélite</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Compra autónoma adicional Obramat</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura 003-0003-452516</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>452516</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>135.00</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PENDIENTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FUERTE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Factura nominativa real no integrada en los 4 pedidos principales. Mampara, muy conectable con la reforma del baño.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
